--- a/docs/compliance/IFRS9_EIR_Amortised_Cost_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_EIR_Amortised_Cost_Compliance_Audit.xlsx
@@ -2723,7 +2723,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 20:26:00 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-08 20:35:36 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/IFRS9_EIR_Amortised_Cost_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_EIR_Amortised_Cost_Compliance_Audit.xlsx
@@ -2723,7 +2723,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 20:35:36 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-08 20:53:33 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/IFRS9_EIR_Amortised_Cost_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_EIR_Amortised_Cost_Compliance_Audit.xlsx
@@ -2723,7 +2723,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 20:53:33 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-08 21:18:12 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/IFRS9_EIR_Amortised_Cost_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_EIR_Amortised_Cost_Compliance_Audit.xlsx
@@ -2723,7 +2723,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 21:18:12 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-09 00:03:12 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/IFRS9_EIR_Amortised_Cost_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_EIR_Amortised_Cost_Compliance_Audit.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baselines" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Audit'!$A$4:$K$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Audit'!$A$4:$K$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Audit'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Findings'!$4:$4</definedName>
   </definedNames>
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="C10" s="13">
-        <f>COUNTA(Audit!$A$5:$A$28)-5</f>
+        <f>COUNTA(Audit!$A$5:$A$27)-5</f>
         <v/>
       </c>
     </row>
@@ -864,7 +864,7 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>5.4.1(a)</t>
+          <t>5.4.1(a), B5.4.7</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
@@ -885,12 +885,12 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>5.4.1(b)</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Cure of a credit-impaired asset</t>
+          <t>Interest on an asset that became credit-impaired</t>
         </is>
       </c>
       <c r="C21" s="16">
@@ -906,12 +906,12 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>Modification of contractual cash flows</t>
+          <t>Cure of a credit-impaired asset</t>
         </is>
       </c>
       <c r="C22" s="16">
@@ -927,12 +927,12 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>5.4.4</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Write-off</t>
+          <t>Modification of contractual cash flows</t>
         </is>
       </c>
       <c r="C23" s="16">
@@ -946,42 +946,42 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>5.4.4, B5.4.9</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Write-off</t>
+        </is>
+      </c>
+      <c r="C24" s="16">
+        <f>Audit!D15</f>
+        <v/>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>B5.4 EFFECTIVE INTEREST METHOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>B5.4.1</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>Fees that are an integral part of the EIR</t>
-        </is>
-      </c>
-      <c r="C25" s="16">
-        <f>Audit!D16</f>
-        <v/>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>Audit row 16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>B5.4.2</t>
+          <t>B5.4.1, B5.4.2</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>Fees that are not an integral part of the EIR</t>
+          <t>Fees that are an integral part of the EIR</t>
         </is>
       </c>
       <c r="C26" s="16">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Expected life and the cash flows considered</t>
+          <t>Fees that are not an integral part of the EIR</t>
         </is>
       </c>
       <c r="C27" s="16">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>Floating-rate instruments</t>
+          <t>The period of amortisation: the expected life</t>
         </is>
       </c>
       <c r="C28" s="16">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Re-estimation of payments or receipts (not a modification)</t>
+          <t>Floating-rate instruments</t>
         </is>
       </c>
       <c r="C29" s="16">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>Modification: recalculate at the original EIR</t>
+          <t>Revised estimates of payments or receipts: the catch-up adjustment</t>
         </is>
       </c>
       <c r="C30" s="16">
@@ -1079,42 +1079,42 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>B5.4.7</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>Interest on a credit-impaired asset</t>
-        </is>
-      </c>
-      <c r="C31" s="16">
-        <f>Audit!D22</f>
-        <v/>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>Audit row 22</t>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>3.3 DERECOGNITION</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>3.3 DERECOGNITION</t>
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>3.3.2</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Extinguishment and substantial modification</t>
+        </is>
+      </c>
+      <c r="C32" s="16">
+        <f>Audit!D23</f>
+        <v/>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 23</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>3.3.2</t>
+          <t>B3.3.6</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>Extinguishment and substantial modification</t>
+          <t>The 10 percent test</t>
         </is>
       </c>
       <c r="C33" s="16">
@@ -1128,42 +1128,42 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>B3.3.6</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>The 10 percent test</t>
-        </is>
-      </c>
-      <c r="C34" s="16">
-        <f>Audit!D25</f>
-        <v/>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>Audit row 25</t>
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>THE RECORD AND ITS PROOF</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>THE RECORD AND ITS PROOF</t>
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>The ledger as the primary record</t>
+        </is>
+      </c>
+      <c r="C35" s="16">
+        <f>Audit!D26</f>
+        <v/>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>Audit row 26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>The ledger as the primary record</t>
+          <t>Governed conventions under maker-checker</t>
         </is>
       </c>
       <c r="C36" s="16">
@@ -1176,57 +1176,36 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>Governed conventions under maker-checker</t>
-        </is>
-      </c>
-      <c r="C37" s="16">
-        <f>Audit!D28</f>
-        <v/>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>Audit row 28</t>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>Findings that need a decision or a fix: see the 'Findings' sheet</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>Findings that need a decision or a fix: see the 'Findings' sheet</t>
+          <t>The acceptance ties read from the system: see the 'Baselines' sheet</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>The acceptance ties read from the system: see the 'Baselines' sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>Source: IFRS 9 Financial Instruments as issued by the IASB, Appendix A (defined terms), section 5.4 (amortised cost measurement), B5.4.1 to B5.4.7 (effective interest method), 5.4.3 and B5.4.6 (modification), 3.3.2 and B3.3.6 (derecognition). Specification: docs/MAIIC_EIR_Engine_Specification_v4_2026-10-07.md sections 3, 4.2, 6, 7.</t>
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>Source: IFRS 9 Financial Instruments as issued by the IASB, Appendix A (defined terms), 5.4.1 to 5.4.4 (amortised cost, modification, write-off), B5.4.1 to B5.4.9 (effective interest method), 3.3.2 and B3.3.6. Specification: docs/MAIIC_EIR_Engine_Specification_v4_2026-10-07.md sections 3, 4.2, 6, 7.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
-  <conditionalFormatting sqref="C14:C38">
+  <conditionalFormatting sqref="C14:C37">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$C14="Done"</formula>
     </cfRule>
@@ -1254,36 +1233,34 @@
     <hyperlink ref="D19" location="'Audit'!A10" display="Audit row 10"/>
     <hyperlink ref="B20" location="'Audit'!A11" display="Purchased or originated credit-impaired assets"/>
     <hyperlink ref="D20" location="'Audit'!A11" display="Audit row 11"/>
-    <hyperlink ref="B21" location="'Audit'!A12" display="Cure of a credit-impaired asset"/>
+    <hyperlink ref="B21" location="'Audit'!A12" display="Interest on an asset that became credit-impaired"/>
     <hyperlink ref="D21" location="'Audit'!A12" display="Audit row 12"/>
-    <hyperlink ref="B22" location="'Audit'!A13" display="Modification of contractual cash flows"/>
+    <hyperlink ref="B22" location="'Audit'!A13" display="Cure of a credit-impaired asset"/>
     <hyperlink ref="D22" location="'Audit'!A13" display="Audit row 13"/>
-    <hyperlink ref="B23" location="'Audit'!A14" display="Write-off"/>
+    <hyperlink ref="B23" location="'Audit'!A14" display="Modification of contractual cash flows"/>
     <hyperlink ref="D23" location="'Audit'!A14" display="Audit row 14"/>
-    <hyperlink ref="B25" location="'Audit'!A16" display="Fees that are an integral part of the EIR"/>
-    <hyperlink ref="D25" location="'Audit'!A16" display="Audit row 16"/>
-    <hyperlink ref="B26" location="'Audit'!A17" display="Fees that are not an integral part of the EIR"/>
+    <hyperlink ref="B24" location="'Audit'!A15" display="Write-off"/>
+    <hyperlink ref="D24" location="'Audit'!A15" display="Audit row 15"/>
+    <hyperlink ref="B26" location="'Audit'!A17" display="Fees that are an integral part of the EIR"/>
     <hyperlink ref="D26" location="'Audit'!A17" display="Audit row 17"/>
-    <hyperlink ref="B27" location="'Audit'!A18" display="Expected life and the cash flows considered"/>
+    <hyperlink ref="B27" location="'Audit'!A18" display="Fees that are not an integral part of the EIR"/>
     <hyperlink ref="D27" location="'Audit'!A18" display="Audit row 18"/>
-    <hyperlink ref="B28" location="'Audit'!A19" display="Floating-rate instruments"/>
+    <hyperlink ref="B28" location="'Audit'!A19" display="The period of amortisation: the expected life"/>
     <hyperlink ref="D28" location="'Audit'!A19" display="Audit row 19"/>
-    <hyperlink ref="B29" location="'Audit'!A20" display="Re-estimation of payments or receipts (not a modification)"/>
+    <hyperlink ref="B29" location="'Audit'!A20" display="Floating-rate instruments"/>
     <hyperlink ref="D29" location="'Audit'!A20" display="Audit row 20"/>
-    <hyperlink ref="B30" location="'Audit'!A21" display="Modification: recalculate at the original EIR"/>
+    <hyperlink ref="B30" location="'Audit'!A21" display="Revised estimates of payments or receipts: the catch-up adjustment"/>
     <hyperlink ref="D30" location="'Audit'!A21" display="Audit row 21"/>
-    <hyperlink ref="B31" location="'Audit'!A22" display="Interest on a credit-impaired asset"/>
-    <hyperlink ref="D31" location="'Audit'!A22" display="Audit row 22"/>
-    <hyperlink ref="B33" location="'Audit'!A24" display="Extinguishment and substantial modification"/>
+    <hyperlink ref="B32" location="'Audit'!A23" display="Extinguishment and substantial modification"/>
+    <hyperlink ref="D32" location="'Audit'!A23" display="Audit row 23"/>
+    <hyperlink ref="B33" location="'Audit'!A24" display="The 10 percent test"/>
     <hyperlink ref="D33" location="'Audit'!A24" display="Audit row 24"/>
-    <hyperlink ref="B34" location="'Audit'!A25" display="The 10 percent test"/>
-    <hyperlink ref="D34" location="'Audit'!A25" display="Audit row 25"/>
-    <hyperlink ref="B36" location="'Audit'!A27" display="The ledger as the primary record"/>
+    <hyperlink ref="B35" location="'Audit'!A26" display="The ledger as the primary record"/>
+    <hyperlink ref="D35" location="'Audit'!A26" display="Audit row 26"/>
+    <hyperlink ref="B36" location="'Audit'!A27" display="Governed conventions under maker-checker"/>
     <hyperlink ref="D36" location="'Audit'!A27" display="Audit row 27"/>
-    <hyperlink ref="B37" location="'Audit'!A28" display="Governed conventions under maker-checker"/>
-    <hyperlink ref="D37" location="'Audit'!A28" display="Audit row 28"/>
-    <hyperlink ref="A39" location="'Findings'!A1" display="Findings that need a decision or a fix: see the 'Findings' sheet"/>
-    <hyperlink ref="A40" location="'Baselines'!A1" display="The acceptance ties read from the system: see the 'Baselines' sheet"/>
+    <hyperlink ref="A38" location="'Findings'!A1" display="Findings that need a decision or a fix: see the 'Findings' sheet"/>
+    <hyperlink ref="A39" location="'Baselines'!A1" display="The acceptance ties read from the system: see the 'Baselines' sheet"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1297,7 +1274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1316,14 +1293,14 @@
     <row r="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>IFRS 9 Financial Instruments - the effective interest rate, amortised cost and the gross carrying amount (Appendix A, 5.4, B5.4, 5.4.3 and B5.4.6, 3.3.2 and B3.3.6) - compliance audit</t>
+          <t>IFRS 9 Financial Instruments - the effective interest rate, amortised cost and the gross carrying amount (Appendix A, 5.4, B5.4, 3.3.2 and B3.3.6) - compliance audit</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Malawi Agricultural and Industrial Investment Company (MAIIC) - IFRS 9 EIR and ECL system - build of 8 October 2026 against specification v4. Prepared 8 October 2026 from the build of specification v4 (commits 32e7d99 to c6353ff): the clean install of eir:bootstrap, the Governance Centre's 48 settings, and the PHPUnit suite (tests/Feature/Eir, tests/Feature/Ebanker). Every approval on the install is the bootstrap's label 'System Bootstrap (automated data-readiness, not a MAIIC approval)'; MAIIC has not approved anything in the system. Reviewer: Dr Thomson Kumwenda (CFO), then Deloitte. Status definitions: see 'Contents'.</t>
+          <t>Malawi Agricultural and Industrial Investment Company (MAIIC) - IFRS 9 EIR and ECL system - build of 14 October 2026 (branch eir_revenue_recognition, commit abe140d) against specification v4. As of 14 October 2026: the code at commit abe140d and the fresh bootstrap maiic_ifrs9_results2 of 13 October 2026 (made before commit 216aee2, so its EIR counts predate the take-on and tranche changes), read with SELECTs only; the Governance Centre catalogue of 61 settings (GovernanceService::catalogue); the PHPUnit suite as written (not run for this audit). Every approval on a bootstrap is the label 'System Bootstrap (automated data-readiness, not a MAIIC approval)'; MAIIC has approved nothing in the system. Reviewer: Dr Thomson Kumwenda (CFO), then Deloitte. Status definitions: see 'Contents'.</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1388,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>The rate that exactly discounts estimated future cash payments or receipts through the expected life of the financial asset to the gross carrying amount; the calculation includes all fees and points paid or received between the parties that are an integral part of the EIR, transaction costs and all other premiums or discounts.</t>
+          <t>The rate that exactly discounts estimated future cash payments or receipts through the expected life of the financial asset to the gross carrying amount, including all fees and points paid or received that are an integral part of the EIR, transaction costs and all other premiums or discounts.</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -1421,33 +1398,33 @@
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>EirCalculationService solves the rate that discounts the approved schedule's cash flows, net of the integral fees, to the initial net investment, on dated flows with the ACT/365 day count; the solver residual and iterations are stored on contract_eir. On the clean install 31 EIRs are solved and 12 locked; 19 are blocked because their fees await a reviewer (B5.4.1 row).</t>
+          <t>EirCalculationService solves the rate that discounts the approved schedule's dated cash flows, net of the reviewed integral fees, to the initial net investment, under the governed day count; later drawdowns enter the vector at their own dates and a tranche facility's schedule follows each drawdown (216aee2). The solver residual and iterations are stored on contract_eir. On the fresh bootstrap: 144 contracts; 14 EIRs solved and locked; 33 generated schedules approved but blocked at the fee gate (their fee lines are not independently reviewed); 73 take-on workbook schedules and 24 contracts with no schedule not yet solved.</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>Spec v4 section 3.1 and 3.3.</t>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). Until 14 October 2026 the row said '31 EIRs solved, 12 locked, 19 blocked' from the 8 October install.</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t>Compliant: the rate is solved from the flows, never typed.</t>
+          <t>Compliant: the rate is solved from the flows, never typed; coverage depends on MAIIC's fee reviews.</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, EIR Calculations: /eir-calculations; Report Hub, EIR as at a Date: /eir-as-at; Contract Profile</t>
+          <t>EIR Calculations, Calculations: /eir-calculations; Blockers: /eir-coverage; EIR Calculations, EIR as at a Date: /eir-as-at</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr"/>
       <c r="J6" s="22" t="inlineStr">
         <is>
-          <t>day_count_basis; compounding_convention</t>
+          <t>day_count</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\EirCalculationWorkflowTest</t>
+          <t>Tests\Feature\Eir\EirCalculationWorkflowTest::test_later_drawdowns_enter_the_eir_vector_at_their_own_dates; Tests\Feature\Eir\TrancheScheduleTest::test_the_schedule_retires_what_was_lent_and_solves_to_the_contractual_rate; Tests\Feature\Eir\ScheduleShapeGovernanceTest::test_the_day_count_is_read_from_the_governance_centre</t>
         </is>
       </c>
     </row>
@@ -1474,33 +1451,33 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>The monthly roll-forward (eir_amortisation: opening, EIR interest, cash received, closing) is produced by eir:run-revenue from the locked EIR, with cash from the ledger's actual receipts where they cover the month (107 of 138 months on the clean install) and from the schedule otherwise; EirAsAtService gives the amortised cost at any date, accruing on actual days inside a month.</t>
+          <t>eir:run-revenue rolls each locked contract forward monthly (eir_amortisation: opening, advances, EIR interest, cash received, closing), opening at the prior month-end (opening_basis), with the arrears at take-on (D39) and cash from the ledger wherever the feed covers the month. On the fresh bootstrap: 13 contracts, 259 monthly rows from July 2024 to September 2026, 255 of them on ledger cash and 4 on the schedule. EirAsAtService gives the amortised cost at any date; inside a month it accrues the part-month at the contractual rate, not the EIR (review item R12, finding F5).</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
-          <t>Spec v4 sections 3, 6.11, 7.1.</t>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). Ledger cash first is decision D35 in code; the cash_source setting is not read.</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>Compliant for the loans with a locked EIR; the loss allowance is applied in the ECL module, not netted here.</t>
+          <t>Compliant at month-ends for the loans with a locked EIR; the loss allowance is applied in the ECL module.</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
         <is>
-          <t>Report Hub, EIR as at a Date: /eir-as-at; Contract Profile; Report Hub, GL Reconciliation (EIR): /eir-reconciliation</t>
+          <t>EIR Calculations, EIR as at a Date: /eir-as-at; EIR Calculations, GL Reconciliation: /eir-reconciliation</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr"/>
       <c r="J7" s="22" t="inlineStr">
         <is>
-          <t>cash_source_precedence (ledger over schedule); plr_mid_period</t>
+          <t>stage3_interest_basis; cash_source (not read: ledger first is fixed by D35)</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\EirAsAtServiceTest::test_a_month_end_reads_the_locked_roll_forward_row; Tests\Feature\Eir\EirRevenueServiceTest</t>
+          <t>Tests\Feature\Eir\EirAsAtServiceTest::test_a_month_end_reads_the_locked_roll_forward_row; Tests\Feature\Eir\EirRevenueServiceTest::test_the_first_month_opens_on_the_value_at_the_month_before</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1504,12 @@
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>The gross carrying amount at any date is the ledger's running balance (sum of every posting on the account to the date), reproduced to the cent against E-Banker's own loan-book report on 2,361 of 2,361 account-months (Baselines sheet).</t>
+          <t>The gross carrying amount at any month-end is the ledger's running balance (method B), equal to E-Banker's own loan-book report on every in-scope account-month: 0 differences over 2 cents in 2,495 account-months on the fresh bootstrap (Baselines sheet). Ledger write-offs reduce it and are not cash (WriteOffClassifier, 220a5a6).</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>Spec v4 sections 6.2 (method B), 6.11.</t>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). Until 14 October 2026 the row said 2,361 account-months.</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -1542,7 +1519,7 @@
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>Report Hub, EIR as at a Date: /eir-as-at; Contract Profile; Data Foundation, Loan Book</t>
+          <t>EIR Calculations, EIR as at a Date: /eir-as-at; Customer &amp; Loan Data, Loan Book</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr"/>
@@ -1577,7 +1554,7 @@
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>Interest revenue is calculated by applying the EIR to the gross carrying amount, except for (a) purchased or originated credit-impaired assets and (b) assets that became credit-impaired after initial recognition, where it is applied to the amortised cost (net of the loss allowance).</t>
+          <t>Interest revenue is calculated by applying the EIR to the gross carrying amount, except for (a) purchased or originated credit-impaired assets and (b) assets that became credit-impaired after initial recognition, where it is applied to the amortised cost.</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -1587,22 +1564,18 @@
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>The roll-forward applies the locked EIR to the opening gross carrying amount for Stage 1 and 2 loans and to the net amount for Stage 3 (interest_basis on each row); the stage is read from the staged loan book, which is why the bootstrap stages before it runs revenue.</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>Spec v4 sections 3, 3.6.</t>
-        </is>
-      </c>
+          <t>The roll-forward applies the EIR to the opening gross carrying amount for Stage 1 and 2 and to the amount net of the opening allowance for Stage 3 (interest_basis on each row; the allowance is the ECL the engine wrote on the prior month's row); the bootstrap stages and runs the ECL before revenue for that reason. A floating-rate loan accrues at the EIR moved with the rate charged (D38, B5.4.5 row).</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr"/>
       <c r="G10" s="22" t="inlineStr">
         <is>
-          <t>Compliant.</t>
+          <t>Compliant for the loans with a locked EIR.</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
         <is>
-          <t>Report Hub, GL Reconciliation (EIR): /eir-reconciliation; Report Hub, EIR as at a Date: /eir-as-at; Contract Profile</t>
+          <t>EIR Calculations, GL Reconciliation: /eir-reconciliation; EIR Calculations, EIR as at a Date: /eir-as-at</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr"/>
@@ -1613,14 +1586,14 @@
       </c>
       <c r="K10" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\EirRevenueServiceTest; Tests\Feature\Eir\StagingServiceTest</t>
+          <t>Tests\Feature\Eir\EirRevenueServiceTest::test_stage_three_nets_the_opening_allowance_the_ecl_engine_wrote; Tests\Feature\Eir\EirRevenueServiceTest::test_stage_three_basis_is_the_governed_setting_in_force_for_the_period</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>5.4.1(a)</t>
+          <t>5.4.1(a), B5.4.7</t>
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr">
@@ -1640,7 +1613,7 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>MAIIC originates its loans and has purchased none; no facility is credit-impaired at origination in the data held (the take-on loans entered E-Banker on 31 July 2024 at their existing balances, which is a migration, not a purchase).</t>
+          <t>MAIIC originates its loans and has purchased none; no facility is credit-impaired at origination in the data held (the take-on loans entered E-Banker on 31 July 2024 at their existing balances, a migration, not a purchase).</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -1655,31 +1628,27 @@
       </c>
       <c r="H11" s="22" t="inlineStr">
         <is>
-          <t>Data Foundation, EIR Data: /eir-data</t>
+          <t>EIR Data, Contract Master: /eir-data</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr"/>
-      <c r="J11" s="22" t="inlineStr">
-        <is>
-          <t>contractual_record; history_before_dec_2025</t>
-        </is>
-      </c>
+      <c r="J11" s="22" t="inlineStr"/>
       <c r="K11" s="22" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>5.4.1(b)</t>
         </is>
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>Cure of a credit-impaired asset</t>
+          <t>Interest on an asset that became credit-impaired</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>When the asset is no longer credit-impaired, interest revenue reverts to the gross basis.</t>
+          <t>When a financial asset becomes credit-impaired after initial recognition, interest revenue is calculated on the amortised cost in subsequent periods.</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -1689,10 +1658,14 @@
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>The stage is re-assessed each period (StagingService); a loan that leaves Stage 3 returns to the gross basis in the next roll-forward row, since interest_basis follows the period's stage.</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr"/>
+          <t>Stage 3 is set by the directive's thresholds (91 days short-term and Mega Farm, 181 otherwise) and the four-missed-instalment trigger, which since 216aee2 reads E-Banker's instalment chart in force at the month-end and net cash; the next roll-forward row is on the net basis (interest_basis NET).</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>Spec v4 section 3.6, decision D31. Until 14 October 2026 this row was labelled B5.4.7, which is the POCI paragraph.</t>
+        </is>
+      </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
           <t>Compliant.</t>
@@ -1700,221 +1673,225 @@
       </c>
       <c r="H12" s="22" t="inlineStr">
         <is>
-          <t>Report Hub, GL Reconciliation (EIR): /eir-reconciliation</t>
+          <t>EIR Calculations, GL Reconciliation: /eir-reconciliation</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr"/>
       <c r="J12" s="22" t="inlineStr">
         <is>
-          <t>dpd_basis; stage3_missed_instalments</t>
+          <t>stage3_interest_basis; dpd_basis; stage3_missed_instalments</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\StagingServiceTest::test_four_unpaid_instalments_lift_a_current_loan_to_stage_3</t>
+          <t>Tests\Feature\Eir\StagingServiceTest::test_four_unpaid_instalments_lift_a_current_loan_to_stage_3; Tests\Feature\Eir\EirRevenueServiceTest::test_stage_three_recognises_net_interest_and_discloses_unwind</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>Modification of contractual cash flows</t>
+          <t>Cure of a credit-impaired asset</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>When the contractual cash flows are renegotiated or modified and the asset is not derecognised, the gross carrying amount is recalculated as the present value of the modified flows at the original EIR and a modification gain or loss is recognised.</t>
+          <t>When the asset is no longer credit-impaired, interest revenue reverts to the gross basis.</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>Partially done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>The roll-forward carries a modification_gain_loss column and rate_reset_events records each reset with its new schedule version; the recalculation at the original EIR is implemented for a schedule re-estimation (B5.4.6 row). The restructured-loan register from E-Banker (the Reschedule Report) is still outstanding from the vendor, so the modifications of 2024 to 2026 are not yet in the system.</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
-        <is>
-          <t>Spec v4 sections 3.2, 5 (Barry / vendor).</t>
-        </is>
-      </c>
+          <t>The stage is re-assessed every period; a cured loan is held at its prior stage for the governed cure period (stage_cure_months) and then returns to Stage 1 or 2, and the roll-forward row of that month is on the gross basis again.</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr"/>
       <c r="G13" s="22" t="inlineStr">
         <is>
-          <t>Partially done: mechanics in place; the restructure history is evidence awaited.</t>
+          <t>Compliant.</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, EIR Calculations: /eir-calculations; Report Hub, EIR as at a Date: /eir-as-at; Contract Profile (modification history)</t>
+          <t>EIR Calculations, GL Reconciliation: /eir-reconciliation; Settings, Staging basis: /setting?tab=staging</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr"/>
       <c r="J13" s="22" t="inlineStr">
         <is>
-          <t>rate_change_classification</t>
+          <t>stage_cure_months; dpd_basis</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\EirAsAtServiceTest::test_a_month_end_reads_the_locked_roll_forward_row</t>
+          <t>Tests\Feature\Eir\StagingServiceTest::test_a_cured_loan_is_held_at_its_prior_stage_for_the_governed_months_and_a_move_up_is_immediate</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>5.4.4</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
+          <t>Modification of contractual cash flows</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>When the contractual cash flows are renegotiated or modified and the asset is not derecognised, recalculate the gross carrying amount as the present value of the modified flows at the original EIR and recognise a modification gain or loss; costs and fees incurred adjust the carrying amount and are amortised over the remaining term.</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>Outstanding</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>Not built: there is no contract_modifications record, no schedule version above 1 and no writer of rate_reset_events (it is only read, by EirAsAtService and the audit trace). The modification_gain_loss column carries only a derecognition without cash (EirRevenueService). E-Banker's reschedule history (RS_02a to RS_02g) landed on 12 October 2026 and is read only for the instalment chart in force used by staging.</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>Until 14 October 2026 this row was Partially done and said the restructure history was awaited from the vendor; it has arrived and the build is Dupleix's (spec P7). The row labelled B5.4.6 repeated this requirement and is folded in here.</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>Outstanding (Dupleix).</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>EIR Calculations, Calculations: /eir-calculations; Blockers: /eir-coverage; EIR Calculations, EIR as at a Date: /eir-as-at</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr"/>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>modification_threshold (not read yet); rate_change_classification (not read yet)</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>5.4.4, B5.4.9</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
           <t>Write-off</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>The gross carrying amount is reduced when there is no reasonable expectation of recovery.</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>The gross carrying amount is reduced when there is no reasonable expectation of recovering a financial asset in its entirety or a portion of it.</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>Evidence needed from MAIIC</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>The loan book carries the write-off through the ECL module; E-Banker's write-off table (DD_16i) returned no rows in the data dictionary of 6 October, so no write-off has been posted in E-Banker since the take-on.</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr"/>
-      <c r="G14" s="22" t="inlineStr">
-        <is>
-          <t>Evidence needed: MAIIC's write-off policy and any write-offs before the take-on.</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
-        <is>
-          <t>Financial Modelling, ECL Calculation: /expected-credit-loss</t>
-        </is>
-      </c>
-      <c r="I14" s="22" t="inlineStr"/>
-      <c r="J14" s="22" t="inlineStr"/>
-      <c r="K14" s="22" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>WriteOffClassifier (220a5a6) treats a credit to a loan account as a write-off when it is type 300, when its batch debits GL 1064, or when it is an ACCOUNT CLOSURE on a status-H account; the loan-book build, the contract inputs and the EIR's ledger cash all use it, so a write-off reduces the gross and is never cash. A write-off not on the loan account goes through the register (/eir-write-offs), proposed by one person and approved by another before it reaches the engines. On the fresh bootstrap: 22 ledger write-offs of 60,778,466.86; the register is empty.</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). Until 14 October 2026 the row said E-Banker's write-off table returned no rows.</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>Evidence needed: MAIIC's write-off policy, Finance's confirmation that status H means written off, and approval of any register entry.</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>EIR Data, Write-offs: /eir-write-offs</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr"/>
+      <c r="J15" s="22" t="inlineStr"/>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Eir\WriteOffTest::test_type_300_is_a_write_off_and_an_ordinary_repayment_is_not; Tests\Feature\Eir\EirRevenueServiceTest::test_a_write_off_reduces_the_gross_but_is_not_cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>B5.4 EFFECTIVE INTEREST METHOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>B5.4.1</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>Fees that are an integral part of the EIR</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>Fees that are an integral part of the EIR of a financial instrument are treated as an adjustment to the EIR (origination fees received as compensation for activities such as evaluating the borrower's financial condition, evaluating guarantees and collateral, negotiating terms, preparing documents and closing the transaction; commitment fees where the loan is likely to be drawn).</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>Partially done</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>The origination fees are read from E-Banker's LOS disbursement charges (87 lines: arrangement 206.3 m, legal 136.7 m, other 9.5 m) into contract_fees as PENDING; the fee rulebook (30 rules, three for E-Banker's own charge names) proposes each one's treatment and a reviewer classifies and a second person reviews under maker-checker; the solver reads only reviewed integral fees. The rulebook is seeded unapproved because approving it is a MAIIC decision, so 19 of 31 solvable EIRs are blocked at the fee gate.</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>Spec v4 sections 3.3, 7.4; the take-on loans' fees are a separate input (O14).</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr">
-        <is>
-          <t>Partially done: the mechanics and the gate are in place; the rulebook and the classifications await MAIIC's reviewer; the take-on fees await Finance.</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
-        <is>
-          <t>Governance Centre, Accounting Rules: /eir-accounting-rules; Fee Classification: /eir-fee-classification; Coverage &amp; Blockers: /eir-coverage</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr"/>
-      <c r="J16" s="22" t="inlineStr">
-        <is>
-          <t>fee_reclass_journal; integral_fee_rulebook</t>
-        </is>
-      </c>
-      <c r="K16" s="22" t="inlineStr">
-        <is>
-          <t>Tests\Feature\Eir\FeeRuleSweepTest; Tests\Feature\Eir\EirReadinessServiceTest</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>B5.4.2</t>
+          <t>B5.4.1, B5.4.2</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>Fees that are not an integral part of the EIR</t>
+          <t>Fees that are an integral part of the EIR</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>Fees for servicing, commitment fees where draw-down is unlikely, and loan syndication fees are not part of the EIR; internal administrative and holding costs are not transaction costs.</t>
+          <t>Fees that are an integral part of the EIR are an adjustment to the EIR: origination fees for evaluating the borrower, guarantees and collateral, negotiating terms, preparing documents and closing; commitment fees where the loan is likely to be drawn.</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Partially done</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>The rulebook's rules for internal administrative and staff cost, recovery and enforcement legal cost and penalty charges propose not-integral, ranked above the origination rules so they can never capture them; a reviewer may reverse any line with a reason.</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr"/>
+          <t>Fee lines land as PENDING from E-Banker's LOS charges, Finance's fee workbook, the take-on workbook and (since 216aee2) the GL fee postings tied to a loan through the drawdown batch (eir:build-gl-fees); fee_source_precedence takes a contract's fees from one source and marks the rest superseded so none counts twice, and the fee GL check sets the fees beside 4871 and 4873. The 30-rule rulebook proposes each line's treatment; a reviewer classifies and a second person reviews; the solver reads only reviewed integral fees. On the fresh bootstrap: 131 LOS fee lines of 1,036.6m, all PENDING; 0 of 30 rules approved; 33 contracts blocked at the fee gate.</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). The take-on fees arrived on 13 October 2026 (O14); the GL route did not run on the fresh bootstrap, which predates it.</t>
+        </is>
+      </c>
       <c r="G17" s="22" t="inlineStr">
         <is>
-          <t>Compliant.</t>
+          <t>Partially done: the mechanics, the source precedence and the gate are in place; the rulebook and the classifications await MAIIC's reviewers.</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>Governance Centre, Accounting Rules: /eir-accounting-rules</t>
+          <t>EIR Rules, Accounting Rules: /eir-accounting-rules; Fee Classification: /eir-fee-classification; EIR Calculations, Calculations: /eir-calculations; Blockers: /eir-coverage</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr"/>
       <c r="J17" s="22" t="inlineStr">
         <is>
-          <t>integral_fee_rulebook</t>
+          <t>fee_source_precedence; fee_gl_reconciliation; fee_reclass_journal (not read yet)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\FeeRuleSweepTest</t>
+          <t>Tests\Feature\Eir\FeeRuleSweepTest::test_unapproved_rules_never_tag_anything; Tests\Feature\Eir\EirReadinessServiceTest::test_pending_fee_blocks_contract_with_named_reason; Tests\Feature\Ebanker\GlFeeRouteTest::test_one_fee_one_source_the_lower_source_is_superseded_and_the_difference_named</t>
         </is>
       </c>
     </row>
@@ -1926,12 +1903,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>Expected life and the cash flows considered</t>
+          <t>Fees that are not an integral part of the EIR</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>The EIR is estimated using the expected life, considering all contractual terms (prepayment, extension, call and similar options) but not expected credit losses; where the cash flows or life cannot be reliably estimated, the contractual terms are used.</t>
+          <t>Fees for servicing, commitment fees where draw-down is unlikely, and loan syndication fees are not part of the EIR.</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -1941,33 +1918,29 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>The version 1 schedule is generated from the contractual terms of the contract master (E-Banker's loan master, the scheme settings, the instalment chart) and approved before the solve; expected prepayment is a governed basis (expected_cashflow_basis, seeded contractual) because MAIIC's two years of history cannot yet support a behavioural estimate.</t>
+          <t>Only reviewed integral fees enter the EIR, so a fee that is not integral never reaches the rate; the rulebook's rules for internal administrative and staff cost, recovery and enforcement legal cost and penalty charges propose not-integral and rank above the origination rules; a reviewer may reverse any line with a reason.</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t>Spec v4 sections 3.2, 4.2.</t>
+          <t>Until 14 October 2026 this row was labelled B5.4.2.</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>Compliant on the contractual basis, which the standard allows where estimates are unreliable.</t>
+          <t>Compliant.</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, EIR Calculations: /eir-calculations; Data Foundation, EIR Data (schedules)</t>
+          <t>EIR Rules, Accounting Rules: /eir-accounting-rules</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr"/>
-      <c r="J18" s="22" t="inlineStr">
-        <is>
-          <t>expected_cashflow_basis; partly_drawn_interest_basis</t>
-        </is>
-      </c>
+      <c r="J18" s="22" t="inlineStr"/>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\ScheduleComparisonTest; Tests\Feature\Eir\ScheduleShapeGovernanceTest</t>
+          <t>Tests\Feature\Eir\FeeRuleSweepTest::test_priority_decides_when_two_rules_could_both_apply; Tests\Feature\Eir\TakeonAndTrancheEirInputTest::test_a_pending_fee_blocks_and_a_superseded_one_does_not</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1952,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>Floating-rate instruments</t>
+          <t>The period of amortisation: the expected life</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>For floating-rate assets, periodic re-estimation of cash flows to reflect movements in market rates alters the EIR; where the asset was recognised at an amount equal to the principal receivable on maturity, re-estimating the future interest payments normally has no significant effect on the carrying amount.</t>
+          <t>Fees, points, transaction costs and premiums or discounts are amortised over the expected life of the instrument, using contractual terms where the cash flows or life cannot be reliably estimated.</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -1994,33 +1967,33 @@
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>The PLR series (48 rows, 26 changes, from E-Banker's PLR master) and each contract's spread over it are held; a reset is recorded as a rate_reset_event with a new schedule version, and the EIR's index component is re-estimated while the locked spread stays (rate_change_classification: a PLR move is a reset, an individual re-pricing is a modification).</t>
+          <t>The version 1 schedule is generated from the contractual terms (contract master, scheme settings, instalment chart, the tranche register for a facility still drawing down) and approved before the solve; a take-on loan's schedule is the take-on workbook's, checked against its own rates before use (takeon_eir_plausibility, 216aee2). No behavioural prepayment estimate is made: expected_cashflow_basis is in the catalogue but no engine reads it, so the basis is contractual in code.</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
         <is>
-          <t>Spec v4 section 3.2.</t>
+          <t>Until 14 October 2026 this row was labelled B5.4.3.</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>Compliant.</t>
+          <t>Compliant on the contractual basis, which the standard allows where estimates are unreliable.</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>Data Foundation, Reference Rates: /eir-reference-rates; Financial Modelling, EIR Calculations: /eir-calculations</t>
+          <t>EIR Calculations, Calculations: /eir-calculations; Blockers: /eir-coverage; EIR Data, Schedule Review: /eir-data?tab=schedules</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr"/>
       <c r="J19" s="22" t="inlineStr">
         <is>
-          <t>rate_change_classification; plr_mid_period</t>
+          <t>partly_drawn_interest_basis; takeon_eir_plausibility; expected_cashflow_basis (not read: contractual in code)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\ReferenceRateImportServiceTest; Tests\Feature\Eir\SpreadDerivationServiceTest</t>
+          <t>Tests\Feature\Eir\ScheduleComparisonTest; Tests\Feature\Eir\ScheduleShapeGovernanceTest::test_the_governed_balance_wise_option_takes_the_drawn_balance_without_reading_the_postings; Tests\Feature\Eir\TakeonAndTrancheEirInputTest::test_a_takeon_solve_the_check_refused_is_named_and_not_used</t>
         </is>
       </c>
     </row>
@@ -2032,44 +2005,48 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>Re-estimation of payments or receipts (not a modification)</t>
+          <t>Floating-rate instruments</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>When an entity revises its estimates of payments or receipts (excluding modifications and changes in expected credit losses), it adjusts the gross carrying amount to the present value of the revised flows at the original EIR and recognises the adjustment in profit or loss.</t>
+          <t>For floating-rate assets, periodic re-estimation of cash flows to reflect movements in market rates alters the effective interest rate.</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Partially done</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>A re-estimated schedule is a new schedule version under the locked original EIR; the roll-forward's modification_gain_loss carries the catch-up and the as-at view lists the schedule version in force on any date.</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr"/>
+          <t>A floating-rate loan's EIR for each month is the locked nominal EIR moved by the change from the rate its schedule was built on to the rate E-Banker charged in the month (EirRevenueService::eirInForce, decision D38), stored as eir_annual on the roll-forward row; the PLR series is held. Not built: rate reset events (no writer of rate_reset_events) and a re-solved schedule at a reset; the mid-month PLR and reset settings are in the catalogue but not read.</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>Until 14 October 2026 this row was labelled B5.4.4 and marked Done.</t>
+        </is>
+      </c>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>Compliant.</t>
+          <t>Partially done: the monthly re-estimation is built; reset events are not.</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
         <is>
-          <t>Report Hub, EIR as at a Date: /eir-as-at; Contract Profile</t>
+          <t>EIR Data, Reference Rates: /eir-reference-rates; EIR Calculations, EIR as at a Date: /eir-as-at</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr"/>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>schedule_approval_control</t>
+          <t>plr_mid_period (not read yet); reset_trigger (not read yet); rate_change_classification (not read yet)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\ScheduleShapeGovernanceTest</t>
+          <t>Tests\Feature\Eir\EirRevenueServiceTest::test_a_floating_rate_loan_accrues_at_the_eir_moved_with_the_rate_charged; Tests\Feature\Eir\EirRevenueServiceTest::test_a_fixed_rate_loan_keeps_its_locked_eir</t>
         </is>
       </c>
     </row>
@@ -2081,121 +2058,113 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>Modification: recalculate at the original EIR</t>
+          <t>Revised estimates of payments or receipts: the catch-up adjustment</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>Where the contractual cash flows are modified and the asset is not derecognised, the new gross carrying amount is the present value of the modified flows discounted at the original EIR; costs and fees adjust the carrying amount and are amortised over the remaining term.</t>
+          <t>When an entity revises its estimates of payments or receipts (excluding modifications and changes in expected credit losses), it adjusts the gross carrying amount to the present value of the revised flows at the original EIR and recognises the adjustment in profit or loss.</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>Partially done</t>
+          <t>Outstanding</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>As 5.4.3: the mechanics exist; the restructure history (E-Banker's Reschedule Report) is awaited from the vendor.</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr"/>
+          <t>Not built: no schedule version above 1 is ever created for a fixed-rate loan and no catch-up adjustment is computed; modification_gain_loss carries only a derecognition without cash. (The floating-rate re-estimation of B5.4.5 is built.)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>Until 14 October 2026 this row was labelled B5.4.5 and marked Done on the basis of mechanics that do not exist.</t>
+        </is>
+      </c>
       <c r="G21" s="22" t="inlineStr">
         <is>
-          <t>Partially done.</t>
+          <t>Outstanding (Dupleix, spec P6).</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, EIR Calculations: /eir-calculations</t>
+          <t>EIR Calculations, EIR as at a Date: /eir-as-at</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr"/>
-      <c r="J21" s="22" t="inlineStr">
-        <is>
-          <t>rate_change_classification</t>
-        </is>
-      </c>
-      <c r="K21" s="22" t="inlineStr">
-        <is>
-          <t>Tests\Feature\Eir\EirAsAtServiceTest</t>
-        </is>
-      </c>
+      <c r="J21" s="22" t="inlineStr"/>
+      <c r="K21" s="22" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>B5.4.7</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>Interest on a credit-impaired asset</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>When a financial asset becomes credit-impaired after initial recognition, interest revenue is applied to the amortised cost in subsequent periods.</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>As 5.4.1: Stage 3 interest is on the net basis in the roll-forward (interest_basis = NET), and the stage follows the directive's thresholds (91 days short-term, 181 otherwise) and the missed-instalment trigger.</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
-        <is>
-          <t>Spec v4 section 3.6, decision D31.</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="inlineStr">
-        <is>
-          <t>Compliant.</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
-        <is>
-          <t>Report Hub, GL Reconciliation (EIR): /eir-reconciliation</t>
-        </is>
-      </c>
-      <c r="I22" s="22" t="inlineStr"/>
-      <c r="J22" s="22" t="inlineStr">
-        <is>
-          <t>stage3_interest_basis; dpd_basis</t>
-        </is>
-      </c>
-      <c r="K22" s="22" t="inlineStr">
-        <is>
-          <t>Tests\Feature\Eir\StagingServiceTest</t>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>3.3 DERECOGNITION</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>3.3 DERECOGNITION</t>
-        </is>
-      </c>
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>3.3.2</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Extinguishment and substantial modification</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>A financial liability (and by analogy an asset whose terms are substantially modified) is derecognised when the terms are substantially different; a modification that is not substantial is accounted for under 5.4.3.</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>Outstanding</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>The 10 percent test of B3.3.6 is not built, and neither is 5.4.3.</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>The reschedule history it needs (RS_02) landed on 12 October 2026; until 14 October 2026 this row waited on it.</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>Outstanding (Dupleix, spec P7).</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>EIR Calculations, Calculations: /eir-calculations; Blockers: /eir-coverage</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr"/>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>modification_threshold (not read yet)</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>3.3.2</t>
+          <t>B3.3.6</t>
         </is>
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>Extinguishment and substantial modification</t>
+          <t>The 10 percent test</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>A financial liability (and by analogy an asset whose terms are substantially modified) is derecognised when the terms are substantially different; a modified asset that is not substantially different is accounted for under 5.4.3.</t>
+          <t>Terms are substantially different if the discounted present value of the cash flows under the new terms, including fees, at the original EIR, differs by at least 10 percent from the discounted present value of the remaining cash flows of the original.</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -2205,193 +2174,152 @@
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>The 10 percent test of B3.3.6 (the present value of the new flows at the original EIR differing by 10 percent or more) is not yet built; every modification is treated under 5.4.3 today.</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>Spec v4 section 5 (open items) names the restructured-loan register as the input.</t>
-        </is>
-      </c>
+          <t>As 3.3.2.</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr"/>
       <c r="G24" s="22" t="inlineStr">
         <is>
-          <t>Outstanding: build the test once the restructure history arrives.</t>
+          <t>Outstanding.</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, EIR Calculations: /eir-calculations</t>
+          <t>EIR Calculations, Calculations: /eir-calculations; Blockers: /eir-coverage</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr"/>
-      <c r="J24" s="22" t="inlineStr"/>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>modification_threshold (not read yet)</t>
+        </is>
+      </c>
       <c r="K24" s="22" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t>B3.3.6</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
-        <is>
-          <t>The 10 percent test</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>Terms are substantially different if the discounted present value of the cash flows under the new terms, including fees, at the original EIR, differs by at least 10 percent from the discounted present value of the remaining cash flows of the original.</t>
-        </is>
-      </c>
-      <c r="D25" s="23" t="inlineStr">
-        <is>
-          <t>Outstanding</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
-        <is>
-          <t>As 3.3.2.</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr"/>
-      <c r="G25" s="22" t="inlineStr">
-        <is>
-          <t>Outstanding.</t>
-        </is>
-      </c>
-      <c r="H25" s="22" t="inlineStr">
-        <is>
-          <t>Financial Modelling, EIR Calculations: /eir-calculations</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr"/>
-      <c r="J25" s="22" t="inlineStr"/>
-      <c r="K25" s="22" t="inlineStr"/>
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>THE RECORD AND ITS PROOF</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>THE RECORD AND ITS PROOF</t>
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>The ledger as the primary record</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>The system's figures must reconcile to the entity's general ledger (IAS 1.15 fair presentation; the auditor's completeness and accuracy assertions).</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Read from the system at generation (Baselines sheet): interest posted January 2025 to July 2026 of 5,293,988,207.06 from the ledger; the derived carrying amount equal to the stored report on 2,495 of 2,495 in-scope account-months; the year-end interest batch contras on 4215 and 4216; the loan GLs at 31 December 2025 equal to the trial balance, with 1050201 and 1050202 off by the accepted exception of section 3.5. The GL reconciliation per period uses the governed tolerance in force for the period.</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>Spec section 9 lists 16 ties; eir:baselines asserts the ones above (finding F6).</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>Compliant for the ties asserted; two pass as accepted exceptions until Finance corrects the keyed openings.</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>EIR Calculations, GL Reconciliation: /eir-reconciliation; Imports &amp; Feeds, E-Banker Loads: /eir-feed</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr"/>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>recon_tolerance; trueup_gl_account (not read yet)</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Ebanker\PackLandingServiceTest; Tests\Feature\Eir\EirGlReconciliationServiceTest::test_the_tolerance_is_the_governed_setting_in_force_for_the_period; eir:bootstrap --verify</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>The ledger as the primary record</t>
+          <t>Governed conventions under maker-checker</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
         <is>
-          <t>The system's figures must reconcile to the entity's general ledger (IAS 1.15 fair presentation; the auditor's completeness and accuracy assertions).</t>
+          <t>Every accounting judgement the engine makes must be a documented, approved policy choice (IAS 8.10 to 8.12), not a constant in code.</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Partially done</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>Interest posted January 2025 to July 2026 of 5,293,988,207.06 from the ledger; the derived carrying amount equal to the stored report on 2,361 of 2,361 account-months; the loan GLs at 31 December 2025 equal to the trial balance to the cent (1050201 and 1050202 off by the accepted exception of section 3.5); the GL reconciliation per period on the screen. The Baselines sheet reads these from the system at generation.</t>
+          <t>61 settings in the Governance Centre catalogue, each with options, a seeded default effective from inception, a proposer and an approver; a calculation that needs a setting with no approved value stops and says so; a locked period keeps the values it was run under. But 20 of the 61 are read by no engine (plr_mid_period, reset_trigger, rate_source_precedence, margin_basis, cash_source, manual_policy_handling, modification_threshold, counter_reset_handling, contractual_record, expected_cashflow_basis, history_before_dec_2025, trueup_gl_account, auditor_export_format, keyman_insurance_treatment, nascomex_preference_shares, staging_rebuttal, rate_change_classification, schedule_approval_control, historic_materiality_assessment, fee_reclass_journal), and some readers fall back to a constant when no value is approved (FliRouteService::setting; LoanBookBuildService::methodInForce falls back to method B; MegaFarmEclService takes a share of 1.0 when the scope text has none).</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>Spec v4 sections 3.4, 3.5, 6.10.2, 9.</t>
+          <t>Until 14 October 2026 the row said 48 settings and was marked Done.</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
         <is>
-          <t>Compliant; two rows pass as accepted exceptions until Finance corrects the keyed openings.</t>
+          <t>Partially done: the mechanism is sound; 20 settings look governed but change nothing, and three readers fail open.</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
         <is>
-          <t>Report Hub, GL Reconciliation (EIR): /eir-reconciliation; Data Foundation, E-Banker Feed: /eir-feed</t>
+          <t>Governance: Governance Centre /eir-governance</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr"/>
       <c r="J27" s="22" t="inlineStr">
         <is>
-          <t>reconciliation_tolerance; trueup_gl_account</t>
+          <t>(all 61 catalogue settings)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Ebanker\PackLandingServiceTest; eir:bootstrap --verify</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>Governed conventions under maker-checker</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>Every accounting judgement the engine makes must be a documented, approved policy choice (IAS 8.10 to 8.12), not a constant in code.</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>48 settings in the Governance Centre, each with options, a seeded default, an effective date, a proposer and an approver; a calculation that needs a setting with no approved value stops and says so; a locked period keeps the values it was run under.</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="inlineStr">
-        <is>
-          <t>Spec v4 section 4.2.</t>
-        </is>
-      </c>
-      <c r="G28" s="22" t="inlineStr">
-        <is>
-          <t>Compliant.</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
-        <is>
-          <t>Governance Centre: /eir-governance</t>
-        </is>
-      </c>
-      <c r="I28" s="22" t="inlineStr"/>
-      <c r="J28" s="22" t="inlineStr">
-        <is>
-          <t>(all)</t>
-        </is>
-      </c>
-      <c r="K28" s="22" t="inlineStr">
-        <is>
-          <t>Tests\Feature\Eir\GovernanceServiceTest; Tests\Feature\Eir\EirGovernanceControllerTest</t>
+          <t>Tests\Feature\Eir\GovernanceServiceTest::test_a_missing_setting_throws_a_named_exception_instead_of_defaulting; Tests\Feature\Eir\EirGovernanceControllerTest</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K28"/>
+  <autoFilter ref="A4:K27"/>
   <mergeCells count="6">
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A25:K25"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A16:K16"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A9:K9"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:D28">
+  <conditionalFormatting sqref="D5:D27">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D5="Done"</formula>
     </cfRule>
@@ -2408,13 +2336,13 @@
       <formula>$D5="Evidence needed from MAIIC"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K28">
+  <conditionalFormatting sqref="K5:K27">
     <cfRule type="expression" priority="6" dxfId="2">
       <formula>AND($D5="Done",$K5="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Done,Partially done,Outstanding,Not applicable, documented,Evidence needed from MAIIC"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2433,7 +2361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2508,29 +2436,29 @@
           <t>F1</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>B5.4.1</t>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>B5.4.1, B5.4.2</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>The fee rulebook is unapproved, so 19 solvable EIRs are blocked</t>
+          <t>The fee rulebook is unapproved, so EIRs are blocked at the fee gate</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>The 30 seeded rules (three for E-Banker's own charge names) carry no approver; the bootstrap reviews only what an approved rule covers, so every LOS charge stays PENDING and the fee gate blocks the contract.</t>
+          <t>The 30 seeded rules carry no approver; every fee line stays PENDING and the fee gate blocks the contract. On the fresh bootstrap 33 contracts with an approved schedule are blocked for this reason and 14 are locked. (Until 14 October 2026 this finding said 19 of 31.)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>19 of 31 loans have no locked EIR; their revenue and amortised cost cannot be produced.</t>
+          <t>The blocked contracts have no locked EIR, so no EIR revenue or amortised cost.</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>A MAIIC reviewer approves the rulebook on the Accounting Rules screen; a second person reviews the classifications; the bootstrap then solves and locks the 19.</t>
+          <t>A MAIIC reviewer approves the rulebook; a second person reviews the classifications; the EIRs are then solved and locked.</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -2552,32 +2480,32 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>B5.4.1</t>
+          <t>B5.4.4</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>The take-on loans' fees are not supplied</t>
+          <t>The take-on loans' EIRs</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>All 78 take-on loans start at the take-on balance because the mapping workbook's fee columns are blank (O14); a blank is never read as fee-free.</t>
+          <t>The take-on fees arrived on 13 October 2026 (the returned mapping workbook, O14) and land as pending lines; commit 216aee2 solves each take-on loan's EIR on its workbook schedule after the plausibility check (takeon_eir_plausibility). On the fresh bootstrap, which predates 216aee2, the 73 take-on workbook schedules are not yet approved or solved.</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>The pre-migration EIR of the 78 cannot be solved from origination; the revenue shift of 2024 is understated for them.</t>
+          <t>The take-on loans carry no locked EIR until the next bootstrap and the fee reviews.</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>Tamanda completes the yellow columns or enters the fees on the Take-on Schedules screen; the build then recomputes from origination where the block and fees exist.</t>
+          <t>Re-run the bootstrap on 216aee2; review the take-on fee lines and the take-on schedules in Schedule Review.</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t>Tamanda Sitimawina</t>
+          <t>Dupleix / Tamanda Sitimawina</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -2599,27 +2527,27 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>The restructure history is not in the system</t>
+          <t>Modification, catch-up and the 10 percent test are not built</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>E-Banker's Reschedule Report and the restructured-loan register are awaited from the vendor; the modification mechanics exist but the 2024 to 2026 modifications are not loaded, and the 10 percent test is not built.</t>
+          <t>E-Banker's reschedule history (RS_02a to RS_02g) landed on 12 October 2026 and is used only for the instalment chart in force; there is no modification record, no schedule version above 1, no catch-up and no 10 percent test. (Until 14 October 2026 this finding said Barry was to obtain the Reschedule Report.)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>Modification gains and losses, and any derecognition, are not recognised.</t>
+          <t>Modification gains and losses, catch-up adjustments and any derecognition are not recognised; IFRS 7.20A and RBM 16(1) wait on the same work.</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
-          <t>Barry obtains the Reschedule Report; the register is loaded by the feed; the 10 percent test is built against it.</t>
+          <t>Dupleix builds the restructure register from RS_02 (Credit confirms the candidates), version N+1 schedules at the original EIR, the B5.4.6 catch-up and the B3.3.6 test.</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>Barry Makumba / Dupleix</t>
+          <t>Dupleix / Credit</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -2670,18 +2598,103 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>A.AC</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Inside a month the as-at report accrues at the contractual rate</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>EirAsAtService accrues the part-month at the contractual rate on actual days and reports it as EIR interest (review item R12); the test asserts that behaviour.</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>An as-at date between month-ends is not at the EIR.</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>Accrue the part-month at the month's EIR and label the contractual figure separately.</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>Dupleix</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>S4, S9</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Settings that change nothing; ties stated but not asserted</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>20 of the 61 catalogue settings are read by no engine and three readers fall back to a constant; spec section 9 lists 16 ties of which eir:baselines asserts the interest total, the method B tie, the two year-end contras and the December 2025 loan GLs.</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>A reviewer may approve a setting that has no effect; the unasserted ties are not proven by --verify.</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>Wire or retire each unread setting and mark it in the catalogue; make the fallbacks fail closed; add the remaining section 9 ties to BaselineService.</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>Dupleix</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Closed,Deferred"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A2" location="'Contents'!A1" display="Back to Contents"/>
-    <hyperlink ref="B5" location="'Audit'!A16" display="B5.4.1"/>
-    <hyperlink ref="B6" location="'Audit'!A16" display="B5.4.1"/>
-    <hyperlink ref="B7" location="'Audit'!A13" display="5.4.3, B5.4.6, 3.3.2"/>
-    <hyperlink ref="B8" location="'Audit'!A27" display="S9"/>
+    <hyperlink ref="B6" location="'Audit'!A19" display="B5.4.4"/>
+    <hyperlink ref="B7" location="'Audit'!A14" display="5.4.3, B5.4.6, 3.3.2"/>
+    <hyperlink ref="B8" location="'Audit'!A26" display="S9"/>
+    <hyperlink ref="B9" location="'Audit'!A7" display="A.AC"/>
+    <hyperlink ref="B10" location="'Audit'!A27" display="S4, S9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2695,7 +2708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -2723,7 +2736,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-09 00:03:12 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-14 08:30:32 from maiic_ifrs9_results2. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2796,7 @@
     <row r="6">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>Derived carrying amount against the stored report (over 2 cents)</t>
+          <t>Derived carrying amount against the stored report, in-scope loan GLs (over 2 cents)</t>
         </is>
       </c>
       <c r="B6" s="22" t="inlineStr">
@@ -2793,7 +2806,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>0 of 2361 account-months</t>
+          <t>0 of 2495 account-months</t>
         </is>
       </c>
       <c r="D6" s="22" t="n">
@@ -2808,20 +2821,24 @@
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>Year-end interest batch contra on 4215</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="n">
-        <v>32956675.55</v>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>32956675.55</v>
+          <t>Mega Farm: account-months whose MF_03 ledger differs from the Loan Book Report (reported, not a test)</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>77540 account-months</t>
+        </is>
       </c>
       <c r="D7" s="22" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E7" s="26">
-        <f>IF(ABS(B7-C7)&lt;=D7,"PASS","FAIL")</f>
+        <f>IF(B7=C7,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="F7" s="22" t="inlineStr"/>
@@ -2829,17 +2846,17 @@
     <row r="8">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>Year-end interest batch contra on 4216</t>
+          <t>Year-end interest batch contra on 4215</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
-        <v>-21733262.7</v>
+        <v>32956675.55</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>-21733262.7</v>
+        <v>32956675.55</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="E8" s="26">
         <f>IF(ABS(B8-C8)&lt;=D8,"PASS","FAIL")</f>
@@ -2850,17 +2867,17 @@
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050101 at 31 Dec 2025 against the trial balance</t>
+          <t>Year-end interest batch contra on 4216</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
-        <v>1368737810.68</v>
+        <v>-21733262.7</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>1368737810.68</v>
+        <v>-21733262.7</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E9" s="26">
         <f>IF(ABS(B9-C9)&lt;=D9,"PASS","FAIL")</f>
@@ -2871,14 +2888,14 @@
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050102 at 31 Dec 2025 against the trial balance</t>
+          <t>Loan book 1050101 at 31 Dec 2025 against the trial balance</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
-        <v>6434045052.56</v>
+        <v>1368737810.68</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>6434045052.56</v>
+        <v>1368737810.68</v>
       </c>
       <c r="D10" s="22" t="n">
         <v>1</v>
@@ -2892,14 +2909,14 @@
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050201 at 31 Dec 2025 against the trial balance (accepted exception, spec 3.5: -400,000.00)</t>
+          <t>Loan book 1050102 at 31 Dec 2025 against the trial balance</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
-        <v>1402393139.46</v>
+        <v>6434045052.56</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>1401993139.46</v>
+        <v>6434045052.56</v>
       </c>
       <c r="D11" s="22" t="n">
         <v>1</v>
@@ -2913,14 +2930,14 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050202 at 31 Dec 2025 against the trial balance (accepted exception, spec 3.5: 1,000,000.00)</t>
+          <t>Loan book 1050201 at 31 Dec 2025 against the trial balance (accepted exception, spec 3.5: -400,000.00)</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
-        <v>3808288656.15</v>
+        <v>1402393139.46</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3809288656.15</v>
+        <v>1401993139.46</v>
       </c>
       <c r="D12" s="22" t="n">
         <v>1</v>
@@ -2934,14 +2951,14 @@
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050401 at 31 Dec 2025 against the trial balance</t>
+          <t>Loan book 1050202 at 31 Dec 2025 against the trial balance (accepted exception, spec 3.5: 1,000,000.00)</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>1827148120.69</v>
+        <v>3808288656.15</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>1827148120.69</v>
+        <v>3809288656.15</v>
       </c>
       <c r="D13" s="22" t="n">
         <v>1</v>
@@ -2952,8 +2969,29 @@
       </c>
       <c r="F13" s="22" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 1050401 at 31 Dec 2025 against the trial balance</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>1827148120.69</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>1827148120.69</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="26">
+        <f>IF(ABS(B14-C14)&lt;=D14,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F14" s="22" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E13">
+  <conditionalFormatting sqref="E5:E14">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E5="PASS"</formula>
     </cfRule>

--- a/docs/compliance/IFRS9_EIR_Amortised_Cost_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_EIR_Amortised_Cost_Compliance_Audit.xlsx
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>eir:run-revenue rolls each locked contract forward monthly (eir_amortisation: opening, advances, EIR interest, cash received, closing), opening at the prior month-end (opening_basis), with the arrears at take-on (D39) and cash from the ledger wherever the feed covers the month. On the fresh bootstrap: 13 contracts, 259 monthly rows from July 2024 to September 2026, 255 of them on ledger cash and 4 on the schedule. EirAsAtService gives the amortised cost at any date; inside a month it accrues the part-month at the contractual rate, not the EIR (review item R12, finding F5).</t>
+          <t>eir:run-revenue rolls each locked contract forward monthly (eir_amortisation: opening, advances, EIR interest, cash received, closing), opening at the prior month-end (opening_basis), with the arrears at take-on (D39) and cash from the ledger wherever the feed covers the month. On the fresh bootstrap: 13 contracts, 259 monthly rows from July 2024 to September 2026, 255 of them on ledger cash and 4 on the schedule. EirAsAtService gives the amortised cost at any date; inside a month it accrues the part-month at the monthly EIR on the amortised cost for the days elapsed and returns the contractual accrual apart (review item R12, finding F5, built 14 October 2026; it had accrued at the contractual rate and called it EIR interest).</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -1755,36 +1755,40 @@
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>Outstanding</t>
+          <t>Partially done</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>Not built: there is no contract_modifications record, no schedule version above 1 and no writer of rate_reset_events (it is only read, by EirAsAtService and the audit trace). The modification_gain_loss column carries only a derecognition without cash (EirRevenueService). E-Banker's reschedule history (RS_02a to RS_02g) landed on 12 October 2026 and is read only for the instalment chart in force used by staging.</t>
+          <t>Built 14 October 2026 (uncommitted in the working tree): the restructure register (RestructureCandidateService finds candidates in RS_02a to RS_02f, the migration worksheet and the rate moves of fixed-rate loans; RestructureRegisterService, one person classifies and another approves), schedule version N+1 from E-Banker's chart after the event, and ModificationAccountingService in the revenue run of the event's month: the modified flows at the original EIR (as re-estimated for a floating loan), the gain or loss, fees through a revised EIR; a month after an unbooked event is refused. The bootstrap and the month-end run the detector only. On the scratch clone maiic_ifrs9_wire of 14 October 2026 (a copy of the restructure build's database, migrated): 70 candidates, none confirmed, so no modification is booked.</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t>Until 14 October 2026 this row was Partially done and said the restructure history was awaited from the vendor; it has arrived and the build is Dupleix's (spec P7). The row labelled B5.4.6 repeated this requirement and is folded in here.</t>
+          <t>Until 14 October 2026 this row was Outstanding: there was no contract_modifications record and no schedule version above 1.</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
         <is>
-          <t>Outstanding (Dupleix).</t>
+          <t>Partially done: built; Credit classifies and approves the candidates, and the IFRS 7.35J disclosure follows in the IFRS 9 note.</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
-          <t>EIR Calculations, Calculations: /eir-calculations; Blockers: /eir-coverage; EIR Calculations, EIR as at a Date: /eir-as-at</t>
+          <t>EIR Calculations, Calculations: /eir-calculations; Blockers: /eir-coverage; EIR Calculations, EIR as at a Date: /eir-as-at; EIR Data, Restructures &amp; Resets: /eir-restructures</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr"/>
       <c r="J14" s="22" t="inlineStr">
         <is>
-          <t>modification_threshold (not read yet); rate_change_classification (not read yet)</t>
-        </is>
-      </c>
-      <c r="K14" s="22" t="inlineStr"/>
+          <t>modification_threshold; rate_change_classification</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Eir\ModificationAccountingTest::test_a_modification_below_the_threshold_resets_the_gross_carrying_amount_at_the_original_eir_with_a_gain_or_loss; Tests\Feature\Eir\ModificationAccountingTest::test_fees_on_a_modification_adjust_the_carrying_amount_and_revise_the_eir; Tests\Feature\Eir\RestructureRegisterTest::test_a_confirmed_modification_needs_two_people_and_loads_schedule_version_two</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
@@ -1967,7 +1971,7 @@
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>The version 1 schedule is generated from the contractual terms (contract master, scheme settings, instalment chart, the tranche register for a facility still drawing down) and approved before the solve; a take-on loan's schedule is the take-on workbook's, checked against its own rates before use (takeon_eir_plausibility, 216aee2). No behavioural prepayment estimate is made: expected_cashflow_basis is in the catalogue but no engine reads it, so the basis is contractual in code.</t>
+          <t>The version 1 schedule is generated from the contractual terms (contract master, scheme settings loaded from the scheme master SM_01 with DD_10 where it lacks a field, instalment chart, the tranche register for a facility still drawing down) and approved before the solve by a person other than the one who prepared it (schedule_approval_control, O18; the bootstrap approves under its own label, recorded on the contract); a take-on loan's schedule is the take-on workbook's, checked against its own rates before use (takeon_eir_plausibility, 216aee2). No behavioural prepayment estimate is made: expected_cashflow_basis is in the catalogue but no engine reads it, so the basis is contractual in code.</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -1988,12 +1992,12 @@
       <c r="I19" s="22" t="inlineStr"/>
       <c r="J19" s="22" t="inlineStr">
         <is>
-          <t>partly_drawn_interest_basis; takeon_eir_plausibility; expected_cashflow_basis (not read: contractual in code)</t>
+          <t>partly_drawn_interest_basis; takeon_eir_plausibility; schedule_approval_control; expected_cashflow_basis (not read: contractual in code)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\ScheduleComparisonTest; Tests\Feature\Eir\ScheduleShapeGovernanceTest::test_the_governed_balance_wise_option_takes_the_drawn_balance_without_reading_the_postings; Tests\Feature\Eir\TakeonAndTrancheEirInputTest::test_a_takeon_solve_the_check_refused_is_named_and_not_used</t>
+          <t>Tests\Feature\Eir\ScheduleComparisonTest; Tests\Feature\Eir\GoLiveControlsTest::test_the_person_who_prepared_a_schedule_cannot_approve_it; Tests\Feature\Eir\GoLiveControlsTest::test_the_scheme_settings_load_from_sm_01_with_dd_10_where_it_lacks_them_and_over_sanction_is_flagged; Tests\Feature\Eir\ScheduleShapeGovernanceTest::test_the_governed_balance_wise_option_takes_the_drawn_balance_without_reading_the_postings; Tests\Feature\Eir\TakeonAndTrancheEirInputTest::test_a_takeon_solve_the_check_refused_is_named_and_not_used</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2024,7 @@
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>A floating-rate loan's EIR for each month is the locked nominal EIR moved by the change from the rate its schedule was built on to the rate E-Banker charged in the month (EirRevenueService::eirInForce, decision D38), stored as eir_annual on the roll-forward row; the PLR series is held. Not built: rate reset events (no writer of rate_reset_events) and a re-solved schedule at a reset; the mid-month PLR and reset settings are in the catalogue but not read.</t>
+          <t>A floating-rate loan's EIR for each month is the locked nominal EIR moved by the change from the rate its schedule was built on to the rate E-Banker charged in the month (EirRevenueService::eirInForce, decision D38), stored as eir_annual on the roll-forward row; the PLR series is held. Since 14 October 2026 (uncommitted) RateResetService records each move of a floating loan's rate on rate_reset_events (a PLR reset, or a spread change for a person to classify, with maker-checker; the bootstrap and the month-end detect only; 323 moves on the scratch clone, none approved). Not built: the mid-month PLR and reset settings are in the catalogue but not read.</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -2030,7 +2034,7 @@
       </c>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>Partially done: the monthly re-estimation is built; reset events are not.</t>
+          <t>Partially done: the monthly re-estimation and the reset register are built; the mid-month PLR setting is not read.</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -2041,12 +2045,12 @@
       <c r="I20" s="22" t="inlineStr"/>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>plr_mid_period (not read yet); reset_trigger (not read yet); rate_change_classification (not read yet)</t>
+          <t>plr_mid_period (not read yet); reset_trigger (not read yet); rate_change_classification</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\EirRevenueServiceTest::test_a_floating_rate_loan_accrues_at_the_eir_moved_with_the_rate_charged; Tests\Feature\Eir\EirRevenueServiceTest::test_a_fixed_rate_loan_keeps_its_locked_eir</t>
+          <t>Tests\Feature\Eir\RateResetTest::test_the_detector_splits_plr_resets_from_spread_changes_and_sends_a_fixed_rate_move_to_the_register; Tests\Feature\Eir\EirRevenueServiceTest::test_a_floating_rate_loan_accrues_at_the_eir_moved_with_the_rate_charged; Tests\Feature\Eir\EirRevenueServiceTest::test_a_fixed_rate_loan_keeps_its_locked_eir</t>
         </is>
       </c>
     </row>
@@ -2068,32 +2072,36 @@
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>Outstanding</t>
+          <t>Partially done</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>Not built: no schedule version above 1 is ever created for a fixed-rate loan and no catch-up adjustment is computed; modification_gain_loss carries only a derecognition without cash. (The floating-rate re-estimation of B5.4.5 is built.)</t>
+          <t>Built 14 October 2026 (uncommitted): a confirmed revised estimate, or a contractual reset of a fixed-rate loan, loads schedule version N+1 and the revenue run of its month sets the gross carrying amount to the revised flows at the original EIR, the catch-up to profit or loss (ModificationAccountingService, treatment CATCH_UP); the IFRS 9 note discloses it in section (h). Nothing is confirmed on the scratch clone, so no catch-up is booked.</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
         <is>
-          <t>Until 14 October 2026 this row was labelled B5.4.5 and marked Done on the basis of mechanics that do not exist.</t>
+          <t>Until 14 October 2026 this row was Outstanding: no schedule version above 1 was created.</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
         <is>
-          <t>Outstanding (Dupleix, spec P6).</t>
+          <t>Partially done: built; the revised estimates wait on Credit's classification of the candidates.</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
         <is>
-          <t>EIR Calculations, EIR as at a Date: /eir-as-at</t>
+          <t>EIR Calculations, EIR as at a Date: /eir-as-at; Reports: IFRS 9 note (FS disclosure) /ifrs9-reports/fs-disclosure (h)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr"/>
       <c r="J21" s="22" t="inlineStr"/>
-      <c r="K21" s="22" t="inlineStr"/>
+      <c r="K21" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Eir\ModificationAccountingTest::test_a_revised_estimate_takes_the_b546_catch_up_and_keeps_the_eir</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
@@ -2120,22 +2128,22 @@
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>Outstanding</t>
+          <t>Partially done</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>The 10 percent test of B3.3.6 is not built, and neither is 5.4.3.</t>
+          <t>Built 14 October 2026 (uncommitted): the 10 percent test of B3.3.6 by analogy against the governed modification_threshold, with the qualitative factors (counterparty, currency, SPPI, instrument) recorded on the register; at or above it, or with a factor, the loan is derecognised and version N+1 recognised at its recorded fair value with a new EIR; a credit-impaired loan derecognised this way is POCI and fails closed (no credit-adjusted EIR is held). Nothing is confirmed on the scratch clone.</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
         <is>
-          <t>The reschedule history it needs (RS_02) landed on 12 October 2026; until 14 October 2026 this row waited on it.</t>
+          <t>Until 14 October 2026 this row was Outstanding.</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
         <is>
-          <t>Outstanding (Dupleix, spec P7).</t>
+          <t>Partially done: built; review item R14 records that the 10 percent test is written for liabilities, so it is MAIIC's governed asset policy.</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -2146,10 +2154,14 @@
       <c r="I23" s="22" t="inlineStr"/>
       <c r="J23" s="22" t="inlineStr">
         <is>
-          <t>modification_threshold (not read yet)</t>
-        </is>
-      </c>
-      <c r="K23" s="22" t="inlineStr"/>
+          <t>modification_threshold</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Eir\ModificationAccountingTest::test_a_change_at_or_above_the_threshold_derecognises_and_fails_closed_without_a_fair_value; Tests\Feature\Eir\ModificationAccountingTest::test_a_qualitative_factor_derecognises_whatever_the_ten_percent_test_says; Tests\Feature\Eir\ModificationAccountingTest::test_a_credit_impaired_loan_derecognised_is_poci_and_fails_closed</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
@@ -2279,17 +2291,17 @@
       </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>61 settings in the Governance Centre catalogue, each with options, a seeded default effective from inception, a proposer and an approver; a calculation that needs a setting with no approved value stops and says so; a locked period keeps the values it was run under. But 20 of the 61 are read by no engine (plr_mid_period, reset_trigger, rate_source_precedence, margin_basis, cash_source, manual_policy_handling, modification_threshold, counter_reset_handling, contractual_record, expected_cashflow_basis, history_before_dec_2025, trueup_gl_account, auditor_export_format, keyman_insurance_treatment, nascomex_preference_shares, staging_rebuttal, rate_change_classification, schedule_approval_control, historic_materiality_assessment, fee_reclass_journal), and some readers fall back to a constant when no value is approved (FliRouteService::setting; LoanBookBuildService::methodInForce falls back to method B; MegaFarmEclService takes a share of 1.0 when the scope text has none).</t>
+          <t>61 settings in the Governance Centre catalogue, each with options, a seeded default effective from inception, a proposer and an approver; a calculation that needs a setting with no approved value stops and says so; a locked period keeps the values it was run under. Since the go-live controls of 14 October 2026 the readers that fell back to a constant stop instead (FliRouteService::setting, LoanBookBuildService::methodInForce and the dpd_basis read, the three Mega Farm settings and the share, the four scenario-set rules, which also read 'No bounds' and 'Not required' as they say), schedule_approval_control is enforced, and the 17 settings still read by no engine are marked 'recorded, not yet applied' in the Governance Centre with what the engine does instead (GovernanceService::notYetApplied; a test fails if an engine reads one of them while it is so marked).</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>Until 14 October 2026 the row said 48 settings and was marked Done.</t>
+          <t>Until 14 October 2026 the row said 48 settings and was marked Done; on 14 October it said 20 settings were read by nothing and three readers failed open.</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
         <is>
-          <t>Partially done: the mechanism is sound; 20 settings look governed but change nothing, and three readers fail open.</t>
+          <t>Partially done: the mechanism is sound and no setting looks governed when it is not; 17 settings await their engines (P5 to P7, O4, O10, O12, O13, O20, O21).</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -2305,7 +2317,7 @@
       </c>
       <c r="K27" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\GovernanceServiceTest::test_a_missing_setting_throws_a_named_exception_instead_of_defaulting; Tests\Feature\Eir\EirGovernanceControllerTest</t>
+          <t>Tests\Feature\Eir\GovernanceServiceTest::test_a_missing_setting_throws_a_named_exception_instead_of_defaulting; Tests\Feature\Eir\GoLiveControlsTest::test_a_setting_marked_not_yet_applied_is_read_by_no_engine; Tests\Feature\Ebanker\LoanBookBuildServiceTest::test_the_method_and_the_dpd_basis_fail_closed_without_an_approved_value; Tests\Feature\FLI\FliRouteServiceTest::test_the_route_stops_when_its_governed_setting_has_no_approved_value; Tests\Feature\Eir\EirGovernanceControllerTest</t>
         </is>
       </c>
     </row>
@@ -2532,27 +2544,27 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>E-Banker's reschedule history (RS_02a to RS_02g) landed on 12 October 2026 and is used only for the instalment chart in force; there is no modification record, no schedule version above 1, no catch-up and no 10 percent test. (Until 14 October 2026 this finding said Barry was to obtain the Reschedule Report.)</t>
+          <t>E-Banker's reschedule history (RS_02a to RS_02g) landed on 12 October 2026 and was used only for the instalment chart in force; there was no modification record, no schedule version above 1, no catch-up and no 10 percent test. Status 14 October 2026: built and wired (uncommitted in the working tree): the restructure register with maker-checker, version N+1, the modification test, the catch-up and derecognition in the revenue run, the detector in the bootstrap and the month-end (detection only), IFRS 7.35J and 20A in the IFRS 9 note, section D of the RBM return. On the scratch clone 70 candidates await classification.</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>Modification gains and losses, catch-up adjustments and any derecognition are not recognised; IFRS 7.20A and RBM 16(1) wait on the same work.</t>
+          <t>Until the candidates are classified no modification is booked.</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
-          <t>Dupleix builds the restructure register from RS_02 (Credit confirms the candidates), version N+1 schedules at the original EIR, the B5.4.6 catch-up and the B3.3.6 test.</t>
+          <t>Credit classifies the candidates and a second person approves; Finance records the fair value of any that derecognise.</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>Dupleix / Credit</t>
+          <t>Credit / Finance</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -2616,17 +2628,17 @@
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>EirAsAtService accrues the part-month at the contractual rate on actual days and reports it as EIR interest (review item R12); the test asserts that behaviour.</t>
+          <t>EirAsAtService accrues the part-month at the contractual rate on actual days and reports it as EIR interest (review item R12); the test asserts that behaviour. Status 14 October 2026: done; the EIR interest is the monthly EIR on the amortised cost for the days elapsed (ties to the revenue run at month-end) and the contractual accrual is returned apart; the test is corrected.</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>An as-at date between month-ends is not at the EIR.</t>
+          <t>A Stage 3 loan's part month is accrued on the gross amortised cost; the month-end row nets the allowance.</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>Accrue the part-month at the month's EIR and label the contractual figure separately.</t>
+          <t>Done.</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -2636,7 +2648,7 @@
       </c>
       <c r="H9" s="22" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -2736,7 +2748,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-14 08:30:32 from maiic_ifrs9_results2. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-14 10:44:21 from maiic_ifrs9_wire. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>
@@ -2990,8 +3002,1424 @@
       </c>
       <c r="F14" s="22" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-09: every file as committed and landed with its manifest rows and SHA-256; 13 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>12 extracts, 111,513 rows</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>12 extracts, 111,513 rows</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E15" s="26">
+        <f>IF(B15=C15,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F15" s="22" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-12: every file as committed and landed with its manifest rows and SHA-256; 2 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>39 extracts, 511,785 rows</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>39 extracts, 511,785 rows</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E16" s="26">
+        <f>IF(B16=C16,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F16" s="22" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-12-p5: every file as committed and landed with its manifest rows and SHA-256; 1 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>8 extracts, 470 rows</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>8 extracts, 470 rows</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E17" s="26">
+        <f>IF(B17=C17,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F17" s="22" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-12-p6: every file as committed and landed with its manifest rows and SHA-256; 0 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>3 extracts, 236 rows</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>3 extracts, 236 rows</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E18" s="26">
+        <f>IF(B18=C18,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F18" s="22" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-13-p7: every file as committed and landed with its manifest rows and SHA-256; 0 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>6 extracts, 32,244 rows</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>6 extracts, 32,244 rows</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E19" s="26">
+        <f>IF(B19=C19,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F19" s="22" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-13-p8: every file as committed and landed with its manifest rows and SHA-256; 6 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>4 extracts, 103 rows</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>4 extracts, 103 rows</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E20" s="26">
+        <f>IF(B20=C20,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F20" s="22" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-14: every file as committed and landed with its manifest rows and SHA-256; 13 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>2 extracts, 426 rows</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>2 extracts, 426 rows</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E21" s="26">
+        <f>IF(B21=C21,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F21" s="22" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: manifest.json (packs 1 and 2, data dictionary, trial balances, take-on): every file as committed and landed with its manifest rows and SHA-256; 3 received files not landed, each with its reason in the manifest; 30 workbooks and scripts, 23 landed by the bootstrap</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>54 extracts, 85,174 rows, 23 workbooks</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>54 extracts, 85,174 rows, 23 workbooks</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E22" s="26">
+        <f>IF(B22=C22,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F22" s="22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Take-on worksheet (CV_10) against the take-on postings of 31 Jul 2024: term loans on the worksheet with take-on postings</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="n">
+        <v>77</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>77</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E23" s="26">
+        <f>IF(ABS(B23-C23)&lt;=D23,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F23" s="22" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Take-on worksheet (CV_10) against the take-on postings of 31 Jul 2024: loans whose principal taken on (301) = NEWDISBURS_AMT, to the cent</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E24" s="26">
+        <f>IF(ABS(B24-C24)&lt;=D24,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F24" s="22" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Take-on worksheet (CV_10) against the take-on postings of 31 Jul 2024: loans whose opening interest (303) = TOTAL_INT_CHARG, to the cent</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E25" s="26">
+        <f>IF(ABS(B25-C25)&lt;=D25,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F25" s="22" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>Take-on worksheet (CV_10) against the take-on postings of 31 Jul 2024: loans whose opening recoveries (305) = TOTA_REPAY_UPTO, to the cent</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E26" s="26">
+        <f>IF(ABS(B26-C26)&lt;=D26,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F26" s="22" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Ledger copy CUMVOUCH_BK240824 (CV_04a) to 31 Dec 2023 against the GL opening balances of 1 Jan 2024 (CV_14), 4 loan GLs: sum of the differences</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E27" s="26">
+        <f>IF(ABS(B27-C27)&lt;=D27,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F27" s="22" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2025-12, MAIIC's loan GLs: carrying amount</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2025-12_maiic_amount)</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>14841212779.54</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E28" s="26">
+        <f>IF(B28=C28,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2025-12, MAIIC's loan GLs: rows</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2025-12_maiic_loans)</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>123</v>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E29" s="26">
+        <f>IF(B29=C29,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2025-12, Mega Farm programme GLs: carrying amount</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2025-12_megafarm_amount)</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>54498560819.6</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E30" s="26">
+        <f>IF(B30=C30,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2025-12, Mega Farm programme GLs: accounts with a balance</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2025-12_megafarm_accounts)</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>3671</v>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E31" s="26">
+        <f>IF(B31=C31,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2026-09, MAIIC's loan GLs: carrying amount</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2026-09_maiic_amount)</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="n">
+        <v>23189580235.43</v>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E32" s="26">
+        <f>IF(B32=C32,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2026-09, MAIIC's loan GLs: rows</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2026-09_maiic_loans)</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>134</v>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E33" s="26">
+        <f>IF(B33=C33,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2026-09, Mega Farm programme GLs: carrying amount</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2026-09_megafarm_amount)</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="n">
+        <v>56180761113.43</v>
+      </c>
+      <c r="D34" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E34" s="26">
+        <f>IF(B34=C34,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2026-09, Mega Farm programme GLs: accounts with a balance</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2026-09_megafarm_accounts)</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="n">
+        <v>3618</v>
+      </c>
+      <c r="D35" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E35" s="26">
+        <f>IF(B35=C35,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Ledger write-offs on MAIIC loans (WriteOffClassifier): postings</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ledger_writeoffs_postings)</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="D36" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E36" s="26">
+        <f>IF(B36=C36,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Ledger write-offs on MAIIC loans (WriteOffClassifier): amount</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ledger_writeoffs_amount)</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="n">
+        <v>60778466.86</v>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E37" s="26">
+        <f>IF(B37=C37,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book: undiscounted</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_undiscounted)</t>
+        </is>
+      </c>
+      <c r="C38" s="25" t="n">
+        <v>3955543846.37</v>
+      </c>
+      <c r="D38" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E38" s="26">
+        <f>IF(B38=C38,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book: discounted at the EIR (booked)</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_discounted)</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="n">
+        <v>2593174242.3</v>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E39" s="26">
+        <f>IF(B39=C39,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book: loans discounted at the EIR</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_discounted_loans)</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="n">
+        <v>56</v>
+      </c>
+      <c r="D40" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E40" s="26">
+        <f>IF(B40=C40,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book, stage 1: discounted</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_stage1_discounted)</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="n">
+        <v>61318291.61</v>
+      </c>
+      <c r="D41" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E41" s="26">
+        <f>IF(B41=C41,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book, stage 2: discounted</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_stage2_discounted)</t>
+        </is>
+      </c>
+      <c r="C42" s="25" t="n">
+        <v>315409106.41</v>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E42" s="26">
+        <f>IF(B42=C42,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book, stage 3: discounted</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_stage3_discounted)</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="n">
+        <v>2216446844.28</v>
+      </c>
+      <c r="D43" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E43" s="26">
+        <f>IF(B43=C43,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, Mega Farm programme (latest run)</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_megafarm_programme)</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E44" s="26">
+        <f>IF(B44=C44,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, Mega Farm: MAIIC's share</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_megafarm_maiic_share)</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E45" s="26">
+        <f>IF(B45=C45,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book: undiscounted</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_undiscounted)</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="n">
+        <v>11569458915.88</v>
+      </c>
+      <c r="D46" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" s="26">
+        <f>IF(B46=C46,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book: discounted at the EIR (booked)</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_discounted)</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="n">
+        <v>7118643553.12</v>
+      </c>
+      <c r="D47" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E47" s="26">
+        <f>IF(B47=C47,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book: loans discounted at the EIR</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_discounted_loans)</t>
+        </is>
+      </c>
+      <c r="C48" s="25" t="n">
+        <v>62</v>
+      </c>
+      <c r="D48" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E48" s="26">
+        <f>IF(B48=C48,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book, stage 1: discounted</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_stage1_discounted)</t>
+        </is>
+      </c>
+      <c r="C49" s="25" t="n">
+        <v>219546033.9</v>
+      </c>
+      <c r="D49" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" s="26">
+        <f>IF(B49=C49,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F49" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book, stage 2: discounted</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_stage2_discounted)</t>
+        </is>
+      </c>
+      <c r="C50" s="25" t="n">
+        <v>183786390.69</v>
+      </c>
+      <c r="D50" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E50" s="26">
+        <f>IF(B50=C50,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book, stage 3: discounted</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_stage3_discounted)</t>
+        </is>
+      </c>
+      <c r="C51" s="25" t="n">
+        <v>6715311128.53</v>
+      </c>
+      <c r="D51" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E51" s="26">
+        <f>IF(B51=C51,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, Mega Farm programme (latest run)</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_megafarm_programme)</t>
+        </is>
+      </c>
+      <c r="C52" s="25" t="n">
+        <v>45782301503.37</v>
+      </c>
+      <c r="D52" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E52" s="26">
+        <f>IF(B52=C52,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, Mega Farm: MAIIC's share</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_megafarm_maiic_share)</t>
+        </is>
+      </c>
+      <c r="C53" s="25" t="n">
+        <v>2289115075.17</v>
+      </c>
+      <c r="D53" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" s="26">
+        <f>IF(B53=C53,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>EIR contracts locked</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (eir_contracts_locked)</t>
+        </is>
+      </c>
+      <c r="C54" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="D54" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" s="26">
+        <f>IF(B54=C54,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>EIR contracts blocked</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (eir_contracts_blocked)</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="D55" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E55" s="26">
+        <f>IF(B55=C55,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F55" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>EIR contracts solved (an EIR computed)</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (eir_contracts_solved)</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="D56" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E56" s="26">
+        <f>IF(B56=C56,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>EIR contracts in the contract master</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (eir_contracts)</t>
+        </is>
+      </c>
+      <c r="C57" s="25" t="n">
+        <v>144</v>
+      </c>
+      <c r="D57" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E57" s="26">
+        <f>IF(B57=C57,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2024: EIR interest recognised</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2024_eir_interest)</t>
+        </is>
+      </c>
+      <c r="C58" s="25" t="n">
+        <v>25532678.7</v>
+      </c>
+      <c r="D58" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E58" s="26">
+        <f>IF(B58=C58,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2024: cash received</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2024_cash_received)</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="n">
+        <v>34200000</v>
+      </c>
+      <c r="D59" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E59" s="26">
+        <f>IF(B59=C59,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F59" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2024: roll-forward rows</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2024_rows)</t>
+        </is>
+      </c>
+      <c r="C60" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="D60" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" s="26">
+        <f>IF(B60=C60,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2025: EIR interest recognised</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2025_eir_interest)</t>
+        </is>
+      </c>
+      <c r="C61" s="25" t="n">
+        <v>663970866.88</v>
+      </c>
+      <c r="D61" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" s="26">
+        <f>IF(B61=C61,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F61" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2025: cash received</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2025_cash_received)</t>
+        </is>
+      </c>
+      <c r="C62" s="25" t="n">
+        <v>1158267060.2</v>
+      </c>
+      <c r="D62" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E62" s="26">
+        <f>IF(B62=C62,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F62" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2025: roll-forward rows</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2025_rows)</t>
+        </is>
+      </c>
+      <c r="C63" s="25" t="n">
+        <v>126</v>
+      </c>
+      <c r="D63" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E63" s="26">
+        <f>IF(B63=C63,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F63" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2026: EIR interest recognised</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2026_eir_interest)</t>
+        </is>
+      </c>
+      <c r="C64" s="25" t="n">
+        <v>544517024.26</v>
+      </c>
+      <c r="D64" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E64" s="26">
+        <f>IF(B64=C64,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F64" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2026: cash received</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2026_cash_received)</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="n">
+        <v>2381610987.63</v>
+      </c>
+      <c r="D65" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" s="26">
+        <f>IF(B65=C65,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F65" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2026: roll-forward rows</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2026_rows)</t>
+        </is>
+      </c>
+      <c r="C66" s="25" t="n">
+        <v>113</v>
+      </c>
+      <c r="D66" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" s="26">
+        <f>IF(B66=C66,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F66" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>RBM return 2026-09: facilities classified loss (paragraph 12 list)</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (rbm_2026-09_loss_facilities)</t>
+        </is>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D67" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E67" s="26">
+        <f>IF(B67=C67,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F67" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>RBM return 2026-09: balance of the loss list</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (rbm_2026-09_loss_balance)</t>
+        </is>
+      </c>
+      <c r="C68" s="25" t="n">
+        <v>1510956083.45</v>
+      </c>
+      <c r="D68" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E68" s="26">
+        <f>IF(B68=C68,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F68" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E14">
+  <conditionalFormatting sqref="E5:E68">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E5="PASS"</formula>
     </cfRule>
